--- a/standalone_apps/form_generator/templates/template-extintores-pr.xlsx
+++ b/standalone_apps/form_generator/templates/template-extintores-pr.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="[$-C0A]dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -190,6 +190,10 @@
       <name val="Arial"/>
       <family val="2"/>
       <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -1664,7 +1668,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2378,6 +2382,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -19941,7 +19948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ303"/>
+  <dimension ref="A1:AR303"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.19921875" customWidth="1" style="90" min="1" max="1"/>
@@ -23002,6 +23009,11 @@
       <c r="AO71" s="221" t="n"/>
       <c r="AP71" s="221" t="n"/>
       <c r="AQ71" s="304" t="n"/>
+      <c r="AR71" s="352" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="13.5" customHeight="1" s="90">
       <c r="A72" s="305" t="n"/>
